--- a/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
+++ b/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
@@ -1372,17 +1372,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">

--- a/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
+++ b/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
@@ -1416,13 +1416,21 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
@@ -1432,7 +1440,11 @@
       <c r="O8" s="6" t="n"/>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="6" t="n"/>
       <c r="U8" s="6" t="n"/>
@@ -1448,13 +1460,21 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
@@ -1464,7 +1484,11 @@
       <c r="O9" s="6" t="n"/>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="6" t="n"/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="6" t="n"/>
       <c r="U9" s="6" t="n"/>
@@ -1480,13 +1504,21 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
@@ -1496,7 +1528,11 @@
       <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="6" t="n"/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
@@ -1512,13 +1548,21 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
@@ -1528,7 +1572,11 @@
       <c r="O11" s="6" t="n"/>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n"/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
@@ -1544,13 +1592,21 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
@@ -1560,7 +1616,11 @@
       <c r="O12" s="6" t="n"/>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n"/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
@@ -1576,13 +1636,21 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
@@ -1592,7 +1660,11 @@
       <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="n"/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
@@ -1608,13 +1680,21 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
@@ -1624,7 +1704,11 @@
       <c r="O14" s="6" t="n"/>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="6" t="n"/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
@@ -1640,13 +1724,21 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
@@ -1656,7 +1748,11 @@
       <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
@@ -1672,13 +1768,21 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
@@ -1688,7 +1792,11 @@
       <c r="O16" s="6" t="n"/>
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="n"/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
@@ -1704,13 +1812,21 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
@@ -1720,7 +1836,11 @@
       <c r="O17" s="6" t="n"/>
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="n"/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
@@ -1736,13 +1856,21 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
@@ -1752,7 +1880,11 @@
       <c r="O18" s="6" t="n"/>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="6" t="n"/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
@@ -1768,13 +1900,21 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
@@ -1784,7 +1924,11 @@
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n"/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
@@ -1800,13 +1944,21 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
@@ -1816,7 +1968,11 @@
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="n"/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
@@ -1832,13 +1988,21 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
@@ -1848,7 +2012,11 @@
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
@@ -1864,13 +2032,21 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
@@ -1880,7 +2056,11 @@
       <c r="O22" s="6" t="n"/>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
@@ -1896,13 +2076,21 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -1912,7 +2100,11 @@
       <c r="O23" s="6" t="n"/>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="n"/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="6" t="n"/>
       <c r="U23" s="6" t="n"/>
@@ -1928,13 +2120,21 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
@@ -1944,7 +2144,11 @@
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="6" t="n"/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="6" t="n"/>
       <c r="U24" s="6" t="n"/>
@@ -1960,13 +2164,21 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
+      <c r="D25" s="5" t="inlineStr"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
@@ -1976,7 +2188,11 @@
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="n"/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="6" t="n"/>
       <c r="U25" s="6" t="n"/>
@@ -1992,13 +2208,21 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
+      <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
@@ -2008,7 +2232,11 @@
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="6" t="n"/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="6" t="n"/>
       <c r="U26" s="6" t="n"/>
@@ -2024,13 +2252,21 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
@@ -2040,7 +2276,11 @@
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n"/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="6" t="n"/>
       <c r="U27" s="6" t="n"/>
@@ -2056,13 +2296,21 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
+      <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
@@ -2072,7 +2320,11 @@
       <c r="O28" s="6" t="n"/>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="n"/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="6" t="n"/>
       <c r="U28" s="6" t="n"/>
@@ -2088,13 +2340,21 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
+      <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
@@ -2104,7 +2364,11 @@
       <c r="O29" s="6" t="n"/>
       <c r="P29" s="6" t="n"/>
       <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="n"/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="6" t="n"/>
       <c r="U29" s="6" t="n"/>
@@ -2120,13 +2384,21 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
+      <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
@@ -2136,7 +2408,11 @@
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="n"/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="6" t="n"/>
       <c r="U30" s="6" t="n"/>
@@ -2152,13 +2428,21 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
+      <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
@@ -2168,7 +2452,11 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
       <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="n"/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
       <c r="U31" s="6" t="n"/>
@@ -2184,13 +2472,21 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
+      <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
@@ -2200,7 +2496,11 @@
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="n"/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
       <c r="U32" s="6" t="n"/>

--- a/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
+++ b/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
@@ -1372,11 +1372,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1416,11 +1436,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1460,11 +1500,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1504,11 +1564,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1548,11 +1628,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1592,11 +1692,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1636,11 +1756,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1680,11 +1820,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1724,11 +1884,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1768,11 +1948,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1812,11 +2012,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1856,11 +2076,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1900,11 +2140,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1944,11 +2204,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1988,11 +2268,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2032,11 +2332,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2076,11 +2396,31 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2120,11 +2460,31 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2164,11 +2524,31 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2208,11 +2588,31 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2252,11 +2652,31 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2296,11 +2716,31 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2340,11 +2780,31 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2384,11 +2844,31 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2428,11 +2908,31 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2472,11 +2972,31 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>177229</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
+++ b/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">

--- a/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
+++ b/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
@@ -1438,22 +1438,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1772029</t>
+          <t>1772030</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1772029</t>
+          <t>1772030</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1502,22 +1502,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>1772029</t>
+          <t>1772031</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1772029</t>
+          <t>1772031</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1566,22 +1566,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>1772029</t>
+          <t>1772032</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1772029</t>
+          <t>1772032</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1628,41 +1628,13 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
@@ -1672,11 +1644,7 @@
       <c r="O11" s="6" t="n"/>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
@@ -1692,41 +1660,13 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
@@ -1736,11 +1676,7 @@
       <c r="O12" s="6" t="n"/>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
@@ -1756,41 +1692,13 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
@@ -1800,11 +1708,7 @@
       <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
@@ -1820,41 +1724,13 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
@@ -1864,11 +1740,7 @@
       <c r="O14" s="6" t="n"/>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
@@ -1884,41 +1756,13 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
@@ -1928,11 +1772,7 @@
       <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
@@ -1948,41 +1788,13 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
@@ -1992,11 +1804,7 @@
       <c r="O16" s="6" t="n"/>
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
@@ -2012,41 +1820,13 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
@@ -2056,11 +1836,7 @@
       <c r="O17" s="6" t="n"/>
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
@@ -2076,41 +1852,13 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
@@ -2120,11 +1868,7 @@
       <c r="O18" s="6" t="n"/>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
@@ -2140,41 +1884,13 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
@@ -2184,11 +1900,7 @@
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
@@ -2204,41 +1916,13 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
@@ -2248,11 +1932,7 @@
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
@@ -2268,41 +1948,13 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
@@ -2312,11 +1964,7 @@
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
@@ -2332,41 +1980,13 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
@@ -2376,11 +1996,7 @@
       <c r="O22" s="6" t="n"/>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
@@ -2396,41 +2012,13 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -2440,11 +2028,7 @@
       <c r="O23" s="6" t="n"/>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R23" s="6" t="n"/>
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="6" t="n"/>
       <c r="U23" s="6" t="n"/>
@@ -2460,41 +2044,13 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
@@ -2504,11 +2060,7 @@
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R24" s="6" t="n"/>
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="6" t="n"/>
       <c r="U24" s="6" t="n"/>
@@ -2524,41 +2076,13 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
@@ -2568,11 +2092,7 @@
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R25" s="6" t="n"/>
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="6" t="n"/>
       <c r="U25" s="6" t="n"/>
@@ -2588,41 +2108,13 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
@@ -2632,11 +2124,7 @@
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R26" s="6" t="n"/>
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="6" t="n"/>
       <c r="U26" s="6" t="n"/>
@@ -2652,41 +2140,13 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
@@ -2696,11 +2156,7 @@
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R27" s="6" t="n"/>
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="6" t="n"/>
       <c r="U27" s="6" t="n"/>
@@ -2716,41 +2172,13 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
@@ -2760,11 +2188,7 @@
       <c r="O28" s="6" t="n"/>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R28" s="6" t="n"/>
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="6" t="n"/>
       <c r="U28" s="6" t="n"/>
@@ -2780,41 +2204,13 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
@@ -2824,11 +2220,7 @@
       <c r="O29" s="6" t="n"/>
       <c r="P29" s="6" t="n"/>
       <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R29" s="6" t="n"/>
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="6" t="n"/>
       <c r="U29" s="6" t="n"/>
@@ -2844,41 +2236,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
@@ -2888,11 +2252,7 @@
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R30" s="6" t="n"/>
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="6" t="n"/>
       <c r="U30" s="6" t="n"/>
@@ -2908,41 +2268,13 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
@@ -2952,11 +2284,7 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
       <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R31" s="6" t="n"/>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
       <c r="U31" s="6" t="n"/>
@@ -2972,41 +2300,13 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>1772029</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
@@ -3016,11 +2316,7 @@
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R32" s="6" t="n"/>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
       <c r="U32" s="6" t="n"/>

--- a/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
+++ b/output/upload/S00022_1772_e연금저축보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AD110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1407,15 +1407,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
@@ -1438,22 +1470,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1772030</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1772030</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1471,15 +1503,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
@@ -1502,22 +1566,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>1772031</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1772031</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1535,15 +1599,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
@@ -1566,22 +1662,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>1772032</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1772032</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1599,15 +1695,47 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
@@ -1628,23 +1756,87 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
@@ -1660,23 +1852,87 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
@@ -1692,23 +1948,87 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
@@ -1724,23 +2044,87 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
@@ -1756,23 +2140,87 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
@@ -1788,23 +2236,87 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
@@ -1820,23 +2332,87 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
@@ -1852,23 +2428,87 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
@@ -1884,23 +2524,87 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
-      <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
@@ -1916,23 +2620,87 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
@@ -1948,23 +2716,87 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
@@ -1980,23 +2812,87 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
@@ -2012,23 +2908,87 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
-      <c r="N23" s="6" t="n"/>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="6" t="n"/>
-      <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="6" t="n"/>
       <c r="U23" s="6" t="n"/>
@@ -2044,23 +3004,87 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-      <c r="M24" s="6" t="n"/>
-      <c r="N24" s="6" t="n"/>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="6" t="n"/>
-      <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="6" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="6" t="n"/>
       <c r="U24" s="6" t="n"/>
@@ -2076,23 +3100,87 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n"/>
-      <c r="N25" s="6" t="n"/>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="6" t="n"/>
       <c r="U25" s="6" t="n"/>
@@ -2108,23 +3196,87 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-      <c r="M26" s="6" t="n"/>
-      <c r="N26" s="6" t="n"/>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="6" t="n"/>
-      <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="6" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="6" t="n"/>
       <c r="U26" s="6" t="n"/>
@@ -2140,23 +3292,87 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
-      <c r="N27" s="6" t="n"/>
-      <c r="O27" s="6" t="n"/>
-      <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="6" t="n"/>
       <c r="U27" s="6" t="n"/>
@@ -2172,23 +3388,87 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-      <c r="M28" s="6" t="n"/>
-      <c r="N28" s="6" t="n"/>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="6" t="n"/>
-      <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="6" t="n"/>
       <c r="U28" s="6" t="n"/>
@@ -2204,23 +3484,87 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
-      <c r="N29" s="6" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="n"/>
-      <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="6" t="n"/>
       <c r="U29" s="6" t="n"/>
@@ -2236,23 +3580,87 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
-      <c r="N30" s="6" t="n"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="6" t="n"/>
       <c r="U30" s="6" t="n"/>
@@ -2268,23 +3676,87 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
-      <c r="M31" s="6" t="n"/>
-      <c r="N31" s="6" t="n"/>
-      <c r="O31" s="6" t="n"/>
-      <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
       <c r="U31" s="6" t="n"/>
@@ -2300,23 +3772,87 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-      <c r="M32" s="6" t="n"/>
-      <c r="N32" s="6" t="n"/>
-      <c r="O32" s="6" t="n"/>
-      <c r="P32" s="6" t="n"/>
-      <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>1772029</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 종신연금형 무배당</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
       <c r="U32" s="6" t="n"/>
@@ -2330,6 +3866,6480 @@
       <c r="AC32" s="6" t="n"/>
       <c r="AD32" s="6" t="n"/>
     </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>55</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>56</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>57</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>58</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>59</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>60</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>61</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>62</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>63</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>64</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>65</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>66</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>67</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>68</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>69</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>70</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>71</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>72</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>73</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>74</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>75</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>76</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>77</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>78</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>79</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1772030</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(10년) 무배당</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>80</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>55</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>56</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>57</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>58</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>59</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>60</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>61</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>62</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>63</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>64</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>65</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>66</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>67</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>68</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>69</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>70</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>71</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>72</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>73</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>74</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>75</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>76</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>77</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>78</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>79</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1772031</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(15년) 무배당</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>80</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>55</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>56</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>57</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>58</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>59</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>60</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>61</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>62</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>63</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>64</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>65</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>66</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>67</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>68</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>69</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>70</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>71</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>72</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>73</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>74</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>75</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>76</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>77</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>78</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>79</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1772032</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>한화생명 e연금저축보험 확정기간연금형(20년) 무배당</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>80</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="R3:AD3"/>
